--- a/data/Blank_Periodic_Table_Base.xlsx
+++ b/data/Blank_Periodic_Table_Base.xlsx
@@ -5,18 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17914\Desktop\Adobe软件制作\自创元素周期表\学术类\Eletronegativity Periodic Table\素材\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17914\Desktop\Adobe软件制作\自创元素周期表\学术类\Ionization Energy Periodic Table\素材\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D1D004-0ACD-4FC3-BF9A-30492D8031A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31738D4-8084-4DF1-818B-3C3DDFC46140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="118" sheetId="3" r:id="rId1"/>
     <sheet name="χ (p)" sheetId="4" r:id="rId2"/>
-    <sheet name="172" sheetId="1" r:id="rId3"/>
-    <sheet name="Color" sheetId="2" r:id="rId4"/>
+    <sheet name="I1" sheetId="5" r:id="rId3"/>
+    <sheet name="Blank" sheetId="6" r:id="rId4"/>
+    <sheet name="172" sheetId="1" r:id="rId5"/>
+    <sheet name="Color" sheetId="2" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,8 +65,21 @@
       <name val="STIX Two Text"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="63">
+  <fills count="126">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -444,6 +459,392 @@
           <color rgb="FFFDDEB2"/>
         </stop>
       </gradientFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE0B0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9AC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF7A6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDD9B8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDDBB5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF1A8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F3A9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA6DFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDD7BC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9F6A7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF0A9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EAB0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9EDDDA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E1F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDED5EA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDEFA9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5EFAC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F0AB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4E2C5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB6E0E7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFECFC7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDDCB4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDDFB0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE2AF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE1AF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE8AC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDECAA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDECAB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDEBAB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F5A7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F3A9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDE7B4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9EDED4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFECEC9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDD9B9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDDDB3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE4AE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE6AD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7A6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3A7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E5B9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDD5BE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDD8BA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDD7BB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDD7BA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDD8B9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EFAC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0EDAD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDD6BD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDDCB3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDDDB2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <gradientFill degree="180">
+        <stop position="0">
+          <color rgb="FFFDD7BC"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFFDDDB3"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDEAAB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3EEAC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF2A8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6A6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFECDCA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDD6BC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFED3C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <gradientFill degree="180">
+        <stop position="0">
+          <color rgb="FFFED3C0"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFFDE0B0"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF2A9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE6B6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="10">
@@ -591,7 +992,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -839,6 +1240,264 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="64" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="65" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="66" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="70" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="70" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="70" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="70" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="70" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="70" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="70" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="71" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="72" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="73" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="74" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="75" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="76" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="71" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="77" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="78" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="79" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="80" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="81" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="82" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="83" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="84" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="85" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="86" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="87" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="88" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="89" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="90" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="91" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="92" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="93" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="90" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="69" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="94" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="95" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="96" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="97" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="98" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="99" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="63" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="88" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="100" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="101" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="74" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="102" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="103" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="102" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="104" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="105" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="106" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="107" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="108" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="109" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="98" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="67" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="72" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="110" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="68" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="111" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="112" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="113" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="114" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="115" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="116" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="117" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="118" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="116" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="119" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="120" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="68" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="73" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="121" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="122" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="123" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="124" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="125" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="87" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -851,16 +1510,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFFED5BF"/>
+      <color rgb="FFFDE2AF"/>
+      <color rgb="FFCAE6B6"/>
+      <color rgb="FFEFF2A9"/>
+      <color rgb="FFFDF0A9"/>
+      <color rgb="FFFDE9AC"/>
+      <color rgb="FFFDEAAB"/>
+      <color rgb="FFFDEBAB"/>
+      <color rgb="FFFDECAB"/>
+      <color rgb="FFFED3C0"/>
       <color rgb="FFFDDEB2"/>
-      <color rgb="FFFED9BA"/>
-      <color rgb="FFF1F4A9"/>
-      <color rgb="FFFEF3A8"/>
-      <color rgb="FFFEEDAB"/>
-      <color rgb="FFFDEAAC"/>
-      <color rgb="FFFDE7AD"/>
-      <color rgb="FFE3EEAD"/>
-      <color rgb="FFFEF6A7"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1429,6 +2088,311 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71E7E0D1-0E63-4FB6-A38B-F9C3E33CFDE7}">
+  <dimension ref="B1:S12"/>
+  <sheetFormatPr defaultRowHeight="50" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="2:19" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:19" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="98"/>
+      <c r="S2" s="9"/>
+    </row>
+    <row r="3" spans="2:19" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="99"/>
+      <c r="C3" s="100"/>
+      <c r="N3" s="101"/>
+      <c r="O3" s="102"/>
+      <c r="P3" s="103"/>
+      <c r="Q3" s="104"/>
+      <c r="R3" s="105"/>
+      <c r="S3" s="106"/>
+    </row>
+    <row r="4" spans="2:19" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="63"/>
+      <c r="C4" s="30"/>
+      <c r="N4" s="107"/>
+      <c r="O4" s="108"/>
+      <c r="P4" s="109"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="111"/>
+      <c r="S4" s="112"/>
+    </row>
+    <row r="5" spans="2:19" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="113"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="115"/>
+      <c r="E5" s="116"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="118"/>
+      <c r="I5" s="119"/>
+      <c r="J5" s="120"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="121"/>
+      <c r="M5" s="122"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="123"/>
+      <c r="P5" s="124"/>
+      <c r="Q5" s="125"/>
+      <c r="R5" s="126"/>
+      <c r="S5" s="127"/>
+    </row>
+    <row r="6" spans="2:19" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="128"/>
+      <c r="C6" s="129"/>
+      <c r="D6" s="130"/>
+      <c r="E6" s="131"/>
+      <c r="F6" s="132"/>
+      <c r="G6" s="133"/>
+      <c r="H6" s="134"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="118"/>
+      <c r="K6" s="135"/>
+      <c r="L6" s="88"/>
+      <c r="M6" s="136"/>
+      <c r="N6" s="90"/>
+      <c r="O6" s="57"/>
+      <c r="P6" s="137"/>
+      <c r="Q6" s="138"/>
+      <c r="R6" s="109"/>
+      <c r="S6" s="139"/>
+    </row>
+    <row r="7" spans="2:19" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="1"/>
+      <c r="C7" s="140"/>
+      <c r="D7" s="154"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="88"/>
+      <c r="G7" s="120"/>
+      <c r="H7" s="120"/>
+      <c r="I7" s="161"/>
+      <c r="J7" s="136"/>
+      <c r="K7" s="159"/>
+      <c r="L7" s="89"/>
+      <c r="M7" s="148"/>
+      <c r="N7" s="114"/>
+      <c r="O7" s="45"/>
+      <c r="P7" s="134"/>
+      <c r="Q7" s="149"/>
+      <c r="R7" s="162"/>
+      <c r="S7" s="150"/>
+    </row>
+    <row r="8" spans="2:19" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="160"/>
+      <c r="C8" s="151"/>
+      <c r="D8" s="165"/>
+      <c r="E8" s="146"/>
+      <c r="F8" s="116"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="155"/>
+      <c r="I8" s="88"/>
+      <c r="J8" s="135"/>
+      <c r="K8" s="166"/>
+      <c r="L8" s="156"/>
+      <c r="M8" s="167"/>
+      <c r="N8" s="134"/>
+      <c r="O8" s="157"/>
+      <c r="P8" s="141"/>
+      <c r="Q8" s="168"/>
+      <c r="R8" s="158"/>
+      <c r="S8" s="159"/>
+    </row>
+    <row r="9" spans="2:19" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="2:19" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E10" s="141"/>
+      <c r="F10" s="141"/>
+      <c r="G10" s="142"/>
+      <c r="H10" s="143"/>
+      <c r="I10" s="141"/>
+      <c r="J10" s="144"/>
+      <c r="K10" s="145"/>
+      <c r="L10" s="114"/>
+      <c r="M10" s="52"/>
+      <c r="N10" s="42"/>
+      <c r="O10" s="146"/>
+      <c r="P10" s="114"/>
+      <c r="Q10" s="114"/>
+      <c r="R10" s="130"/>
+      <c r="S10" s="147"/>
+    </row>
+    <row r="11" spans="2:19" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E11" s="163"/>
+      <c r="F11" s="153"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="152"/>
+      <c r="I11" s="130"/>
+      <c r="J11" s="146"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="130"/>
+      <c r="N11" s="153"/>
+      <c r="O11" s="68"/>
+      <c r="P11" s="115"/>
+      <c r="Q11" s="115"/>
+      <c r="R11" s="131"/>
+      <c r="S11" s="164"/>
+    </row>
+    <row r="12" spans="2:19" ht="50" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AAE35A5-E90A-48A2-AEC8-880294095330}">
+  <dimension ref="B1:S12"/>
+  <sheetFormatPr defaultRowHeight="50" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="2:19" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:19" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="91"/>
+      <c r="S2" s="93"/>
+    </row>
+    <row r="3" spans="2:19" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="92"/>
+      <c r="C3" s="94"/>
+      <c r="N3" s="95"/>
+      <c r="O3" s="93"/>
+      <c r="P3" s="93"/>
+      <c r="Q3" s="93"/>
+      <c r="R3" s="93"/>
+      <c r="S3" s="93"/>
+    </row>
+    <row r="4" spans="2:19" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="93"/>
+      <c r="C4" s="93"/>
+      <c r="N4" s="96"/>
+      <c r="O4" s="95"/>
+      <c r="P4" s="93"/>
+      <c r="Q4" s="93"/>
+      <c r="R4" s="93"/>
+      <c r="S4" s="97"/>
+    </row>
+    <row r="5" spans="2:19" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="83"/>
+      <c r="K5" s="83"/>
+      <c r="L5" s="83"/>
+      <c r="M5" s="83"/>
+      <c r="N5" s="83"/>
+      <c r="O5" s="84"/>
+      <c r="P5" s="85"/>
+      <c r="Q5" s="83"/>
+      <c r="R5" s="83"/>
+      <c r="S5" s="83"/>
+    </row>
+    <row r="6" spans="2:19" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="83"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="83"/>
+      <c r="L6" s="83"/>
+      <c r="M6" s="83"/>
+      <c r="N6" s="83"/>
+      <c r="O6" s="83"/>
+      <c r="P6" s="84"/>
+      <c r="Q6" s="85"/>
+      <c r="R6" s="83"/>
+      <c r="S6" s="83"/>
+    </row>
+    <row r="7" spans="2:19" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="83"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="83"/>
+      <c r="J7" s="83"/>
+      <c r="K7" s="83"/>
+      <c r="L7" s="83"/>
+      <c r="M7" s="83"/>
+      <c r="N7" s="83"/>
+      <c r="O7" s="83"/>
+      <c r="P7" s="83"/>
+      <c r="Q7" s="84"/>
+      <c r="R7" s="86"/>
+      <c r="S7" s="83"/>
+    </row>
+    <row r="8" spans="2:19" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="83"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="83"/>
+      <c r="K8" s="83"/>
+      <c r="L8" s="83"/>
+      <c r="M8" s="83"/>
+      <c r="N8" s="83"/>
+      <c r="O8" s="83"/>
+      <c r="P8" s="83"/>
+      <c r="Q8" s="87"/>
+      <c r="R8" s="86"/>
+      <c r="S8" s="83"/>
+    </row>
+    <row r="9" spans="2:19" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="2:19" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="83"/>
+      <c r="J10" s="83"/>
+      <c r="K10" s="83"/>
+      <c r="L10" s="83"/>
+      <c r="M10" s="83"/>
+      <c r="N10" s="83"/>
+      <c r="O10" s="83"/>
+      <c r="P10" s="83"/>
+      <c r="Q10" s="83"/>
+      <c r="R10" s="83"/>
+      <c r="S10" s="83"/>
+    </row>
+    <row r="11" spans="2:19" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="83"/>
+      <c r="J11" s="83"/>
+      <c r="K11" s="83"/>
+      <c r="L11" s="83"/>
+      <c r="M11" s="83"/>
+      <c r="N11" s="83"/>
+      <c r="O11" s="83"/>
+      <c r="P11" s="83"/>
+      <c r="Q11" s="83"/>
+      <c r="R11" s="83"/>
+      <c r="S11" s="83"/>
+    </row>
+    <row r="12" spans="2:19" ht="50" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:S16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="50" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -1644,7 +2608,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:K2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="50" customHeight="1" x14ac:dyDescent="0.3"/>
